--- a/三電系統開發/V3補充_電池充電器拆分訂閱模型_20260921.xlsx
+++ b/三電系統開發/V3補充_電池充電器拆分訂閱模型_20260921.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="電池訂閱費" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="輪內可拆vs車架可拆" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="護城河" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日本付款路徑" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -135,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -215,6 +216,9 @@
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4672,4 +4676,1112 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F62"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>日本三條付款路徑：通路零利率分期／法人租賃 B2B2C／ふるさと納税</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>日本沒有德國 JobRad 型薪資扣抵制度；公司貸與自行車屬現物給與、全額課稅。本表以配置 D（力矩版）PB 通路零售價與 202Wh 電池訂閱為基準。JPY。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>A. 假設（藍字可改）</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>參數</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>來源 / 說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>車體零售價（平地版，PB 通路，税込）</t>
+        </is>
+      </c>
+      <c r="B6" s="26">
+        <f>入手價!B30</f>
+        <v>48666.11517898195</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>入手價表情境 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>車體零售價（坡地／載童版，税込，估）</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>前次分析：扭力 + 20 吋 + 45 N·m 馬達 + 後碟 + 子乗せ車架，PB 通路約 ¥58,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>電池月費（202Wh）</t>
+        </is>
+      </c>
+      <c r="B8" s="26">
+        <f>電池訂閱費!C61</f>
+        <v>1280.0</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>電池訂閱費表</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>電池月費（360Wh，載童版）</t>
+        </is>
+      </c>
+      <c r="B9" s="26">
+        <f>電池訂閱費!D61</f>
+        <v>1680.0</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>電池訂閱費表</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>分期回數</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>JACCS／Orico ショッピングローン；Panasonic 官網、ハヤサカ最多 36 回無金利</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>消費者分期利率（無金利活動）</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>通路負擔金利</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>通路負擔之分期手數料率（佔本金）</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>假設：36 回無金利活動由通路支付金融公司約 8–12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>NORUDE ViVi SX 整車訂閱月費</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>2890</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>V3 分頁 9；36 月 ¥104,040，期末還車</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>NORUDE 子乗せ月費</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>5690</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>V3 分頁 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>員工邊際稅率（所得稅 + 住民稅）</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>年收 500–700 萬圓區間概算；用於現物給與課稅</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>法人租賃：年利率</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>假設</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>法人租賃：期末殘值率（車體）</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>假設；中國製車在日本二手市場近乎無行情</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>法人租賃：保養與保險（¥/月）</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>假設；Yamaha PAS リース含保養保險</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>法人通路：訂閱呆帳率</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>公司統一請款</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>法人通路：訂閱 CAC（¥）</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>B2B2C 通路，趨近零</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>ふるさと納税：返礼品率上限</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>總務省基準：返礼品 ≤ 寄付額 3 割、含送料事務 ≤ 5 割</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>ふるさと納税：自己負担額</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>控除上限內之固定自付</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>ふるさと納税：返礼品內含電池訂閱月數</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>假設：車體 + 首年電池訂閱券作為一組返礼品</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>ふるさと納税：日本最終組裝加價（¥/台）</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>假設：地場產品基準要求製造主要部分在地；待驗證</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>自治體子乗せ補助（¥）</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>赤穂市 ¥4 萬、輕井澤町 ¥5 萬、廣島府中町 2026 新設；多要求型式認定／BAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>B. 消費者視角：每月支出與 3 年總成本（平地版，202Wh）</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>路徑</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>月付（¥）</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>前置費用（¥）</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>3 年總支出（¥）</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>期末車體歸屬</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>① 通路零利率分期 36 回 + 電池訂閱</t>
+        </is>
+      </c>
+      <c r="B29" s="13">
+        <f>B6*(1+B11)/B10+B8</f>
+        <v>2631.8365327494985</v>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="24">
+        <f>B6*(1+B11)+B8*36</f>
+        <v>94746.11517898194</v>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>消費者</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>主打對比：與 NORUDE 同價位，但車歸自己、電池永遠有效</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>② A 法人付電池訂閱、員工自買車體（分期）</t>
+        </is>
+      </c>
+      <c r="B30" s="13">
+        <f>B6/B10+B8*B15</f>
+        <v>1607.8365327494985</v>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="24">
+        <f>B30*36</f>
+        <v>57882.11517898194</v>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>員工</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>員工月付 = 車體分期 + 電池訂閱現物給與之稅負；公司付電池月費</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>② B 法人全額租賃（車體 + 電池 + 保養），員工負擔課稅</t>
+        </is>
+      </c>
+      <c r="B31" s="13">
+        <f>((B6*(1-B17))/B10+B6*B16/12+B8+B18)*B15</f>
+        <v>599.8856718773948</v>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="24">
+        <f>B31*36</f>
+        <v>21595.884187586213</v>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>公司（期末殘值）</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>公司月付見 C 段；員工僅負擔現物給與稅</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>③ ふるさと納税（車體 + 首年電池訂閱券）</t>
+        </is>
+      </c>
+      <c r="B32" s="13">
+        <f>B8*(36-B23)/36</f>
+        <v>853.3333333333334</v>
+      </c>
+      <c r="C32" s="12">
+        <f>B22</f>
+        <v>2000.0</v>
+      </c>
+      <c r="D32" s="24">
+        <f>B22+B8*(36-B23)</f>
+        <v>32720.0</v>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>消費者</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>前提：寄付額落在個人控除上限內（見 D 段），且產品符合地場產品基準</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>對照：NORUDE ViVi SX 整車訂閱</t>
+        </is>
+      </c>
+      <c r="B33" s="12">
+        <f>B13</f>
+        <v>2890.0</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>3520</v>
+      </c>
+      <c r="D33" s="12">
+        <f>B13*36+C33</f>
+        <v>107560.0</v>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>NORUDE（還車）</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>事務手數料 ¥3,520；盜難補償 ¥700/月另計</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>對照：PELTECH 型式認定車買斷 ¥89,980</t>
+        </is>
+      </c>
+      <c r="B34" s="12">
+        <f>89980/36</f>
+        <v>2499.4444444444443</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>89980</v>
+      </c>
+      <c r="D34" s="12">
+        <f>89980+5000*3</f>
+        <v>104980.0</v>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>消費者</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>含年維護 ¥5,000；第 4 年換電池 ¥35,000 未計入 3 年</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>① 對 NORUDE 之 3 年差額（負值 = 本案較省）</t>
+        </is>
+      </c>
+      <c r="D35" s="13">
+        <f>D29-D33</f>
+        <v>-12813.884821018059</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>且車體歸消費者</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>B-2. 載童版（360Wh）：分期 + 自治體補助</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>路徑</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>月付（¥）</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>前置費用（¥）</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>3 年總支出（¥）</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>期末車體歸屬</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>① 載童版分期 36 回 + 360Wh 訂閱</t>
+        </is>
+      </c>
+      <c r="B39" s="13">
+        <f>B7/B10+B9</f>
+        <v>3291.1111111111113</v>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="24">
+        <f>B7+B9*36</f>
+        <v>118480.0</v>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>消費者</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>對照 NORUDE 子乗せ ¥5,690/月、Panasonic Gyutto ¥170,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>① 載童版 + 自治體補助（補助後車體一次付清）</t>
+        </is>
+      </c>
+      <c r="B40" s="13">
+        <f>B9</f>
+        <v>1680.0</v>
+      </c>
+      <c r="C40" s="12">
+        <f>MAX(B7-B25,0)</f>
+        <v>18000.0</v>
+      </c>
+      <c r="D40" s="24">
+        <f>C40+B9*36</f>
+        <v>78480.0</v>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>消費者</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>限有補助之自治體；須型式認定 + BAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>對照：NORUDE 子乗せ</t>
+        </is>
+      </c>
+      <c r="B41" s="12">
+        <f>B14</f>
+        <v>5690.0</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>3520</v>
+      </c>
+      <c r="D41" s="12">
+        <f>B14*36+C41</f>
+        <v>208360.0</v>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>NORUDE（還車）</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>C. 營運商／通路視角：每戶 36 月淨值（電池訂閱）與車體通路成本</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>路徑</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>訂閱月費（¥）</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>呆帳率</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>CAC（¥）</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>36 月單戶淨值（¥）</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>車體側成本 / 說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>① 通路分期（B2C）</t>
+        </is>
+      </c>
+      <c r="B45" s="12">
+        <f>B8</f>
+        <v>1280.0</v>
+      </c>
+      <c r="C45" s="29">
+        <f>假設!$B$75</f>
+        <v>0.03</v>
+      </c>
+      <c r="D45" s="26">
+        <f>假設!$B$83</f>
+        <v>3000.0</v>
+      </c>
+      <c r="E45" s="13">
+        <f>(B8/(1+假設!$B$74)*(1-假設!$B$75-假設!$B$76)-(假設!$B$78+假設!$B$79+假設!$B$77)-電池訂閱費!C54-電池訂閱費!C53)*假設!$B$82+電池訂閱費!C49*假設!$B$84-電池訂閱費!C51-假設!$B$83</f>
+        <v>11153.926169599987</v>
+      </c>
+      <c r="F45" s="6" t="str">
+        <f>"車體通路須負擔分期手數料 ¥"&amp;TEXT(B6*B12,"#,##0")&amp;"/台（佔零售 "&amp;TEXT(B12,"0%")&amp;"）"</f>
+        <v>車體通路須負擔分期手數料 ¥3,893/台（佔零售 8%）</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>② 法人通路（B2B2C）</t>
+        </is>
+      </c>
+      <c r="B46" s="12">
+        <f>B8</f>
+        <v>1280.0</v>
+      </c>
+      <c r="C46" s="29">
+        <f>B19</f>
+        <v>0.01</v>
+      </c>
+      <c r="D46" s="26">
+        <f>B20</f>
+        <v>1000.0</v>
+      </c>
+      <c r="E46" s="13">
+        <f>(B8/(1+假設!$B$74)*(1-B19-假設!$B$76)-(假設!$B$78+假設!$B$79+假設!$B$77)-電池訂閱費!C54-電池訂閱費!C53)*假設!$B$82+電池訂閱費!C49*假設!$B$84-電池訂閱費!C51-B20</f>
+        <v>13991.74435141817</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>公司統一請款、呆帳趨近零；Yamaha PAS リース 3 台起、NORUDE for Biz 為現成對照</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>③ ふるさと納税（首年由自治體支付，次年起 B2C）</t>
+        </is>
+      </c>
+      <c r="B47" s="12">
+        <f>B8</f>
+        <v>1280.0</v>
+      </c>
+      <c r="C47" s="29">
+        <f>假設!$B$75</f>
+        <v>0.03</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="13">
+        <f>(B8/(1+假設!$B$74)*(1-假設!$B$75-假設!$B$76)-(假設!$B$78+假設!$B$79+假設!$B$77)-電池訂閱費!C54-電池訂閱費!C53)*假設!$B$82+電池訂閱費!C49*假設!$B$84-電池訂閱費!C51-0</f>
+        <v>14153.926169599987</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>CAC 為零（自治體通路）；但須在地組裝加價、且首年訂閱以躉售價賣給自治體</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>② 對 ① 之單戶淨值增幅</t>
+        </is>
+      </c>
+      <c r="E48" s="24">
+        <f>E46-E45</f>
+        <v>2837.818181818184</v>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>呆帳與 CAC 下降的合計效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>② B 公司月付（全額租賃）</t>
+        </is>
+      </c>
+      <c r="B49" s="24">
+        <f>((B6*(1-B17))/B10+B6*B16/12+B8+B18)</f>
+        <v>2999.4283593869736</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>＝ 車體 ×(1−殘值)÷36 + 利息 + 電池月費 + 保養；對照 MOVE.eBike 法人月額 ¥14,000 起</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>D. ふるさと納税可行性檢核：需要的寄付額與年收門檻</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>值（¥）</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr"/>
+      <c r="D52" s="5" t="inlineStr"/>
+      <c r="E52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>返礼品價值 = 車體 + 首年電池訂閱 + 在地組裝加價</t>
+        </is>
+      </c>
+      <c r="B53" s="12">
+        <f>B6+B8*B23+B24</f>
+        <v>70026.11517898194</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>以零售價計（自治體調達價通常低於零售）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>所需寄付額 = 返礼品價值 ÷ 30%</t>
+        </is>
+      </c>
+      <c r="B54" s="13">
+        <f>B53/B21</f>
+        <v>233420.38392993982</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>總務省 3 割規則</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>消費者實際成本（寄付在控除上限內）</t>
+        </is>
+      </c>
+      <c r="B55" s="12">
+        <f>B22</f>
+        <v>2000.0</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>¥2,000 自付；其餘為所得稅與住民稅扣除</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>年收（萬圓，單身無扶養）</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>控除上限概算（¥）</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>可否全額扣除</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>超出部分（¥）</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr"/>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>28000</v>
+      </c>
+      <c r="C57" s="30" t="str">
+        <f>IF(B57&gt;=$B$54,"可","否")</f>
+        <v>否</v>
+      </c>
+      <c r="D57" s="12">
+        <f>MAX($B$54-B57,0)</f>
+        <v>205420.38392993982</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>控除上限為概算（ふるさと納税ポータル試算），實際依家庭狀況；超出部分為消費者自付</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>61000</v>
+      </c>
+      <c r="C58" s="30" t="str">
+        <f>IF(B58&gt;=$B$54,"可","否")</f>
+        <v>否</v>
+      </c>
+      <c r="D58" s="12">
+        <f>MAX($B$54-B58,0)</f>
+        <v>172420.38392993982</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>控除上限為概算（ふるさと納税ポータル試算），實際依家庭狀況；超出部分為消費者自付</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="B59" s="7" t="n">
+        <v>108000</v>
+      </c>
+      <c r="C59" s="30" t="str">
+        <f>IF(B59&gt;=$B$54,"可","否")</f>
+        <v>否</v>
+      </c>
+      <c r="D59" s="12">
+        <f>MAX($B$54-B59,0)</f>
+        <v>125420.38392993982</v>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>控除上限為概算（ふるさと納税ポータル試算），實際依家庭狀況；超出部分為消費者自付</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>176000</v>
+      </c>
+      <c r="C60" s="30" t="str">
+        <f>IF(B60&gt;=$B$54,"可","否")</f>
+        <v>否</v>
+      </c>
+      <c r="D60" s="12">
+        <f>MAX($B$54-B60,0)</f>
+        <v>57420.383929939824</v>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>控除上限為概算（ふるさと納税ポータル試算），實際依家庭狀況；超出部分為消費者自付</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B61" s="7" t="n">
+        <v>389000</v>
+      </c>
+      <c r="C61" s="30" t="str">
+        <f>IF(B61&gt;=$B$54,"可","否")</f>
+        <v>可</v>
+      </c>
+      <c r="D61" s="12">
+        <f>MAX($B$54-B61,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>控除上限為概算（ふるさと納税ポータル試算），實際依家庭狀況；超出部分為消費者自付</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>判讀</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>車體便宜反而讓ふるさと納税不划算：寄付額是產品價值的 3.3 倍，只有高年收者能全額扣除；且地場產品基準要求在地製造，達方無日本工廠。此路徑僅在「日本最終組裝 + 鎖定年收 1,000 萬圓以上家庭」時成立。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/三電系統開發/V3補充_電池充電器拆分訂閱模型_20260921.xlsx
+++ b/三電系統開發/V3補充_電池充電器拆分訂閱模型_20260921.xlsx
@@ -13,6 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="輪內可拆vs車架可拆" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="護城河" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日本付款路徑" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="三變體" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="五年財務" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -136,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -219,6 +221,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5784,4 +5792,2696 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>三個產品變體：平地版／日本平地版／坡地載童版</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>同一車體平台，差異化延到總裝段。材料增額對配置 C（不含電池、不含充電器）計；RMB。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>A. 規格矩陣</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>平地版（歐洲／台灣）</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>日本平地版</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>坡地載童版（日本、坡地城市）</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>感測</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>踏頻 + IMU + 相電流估算（B 方案）</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>中軸扭力感測（法規）</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>中軸扭力感測</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>日本助力比以人力為分母，踏頻不能取證</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>控制邏輯</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>速度保持：目標 20/22/25 km/h，22–25 線性衰減</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>2:1 → 0 線性遞減（10–24 km/h）</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>同日本平地版</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>兩套韌體皆鎖 OTP，出廠依市場燒錄</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>輪徑／齒比</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>26 吋或 700c、44/16</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>26 吋、44/16</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>20–24 吋、42/18</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>小輪徑 + 低齒比補單速在坡地的踏頻與扭矩</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>馬達</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>商品化 250W 齒輪輪轂 30–32 N·m</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>同左</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>40–45 N·m 級齒輪輪轂，含溫度感測與降額</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>載童 125 kg 爬 10% 坡需 33 N·m（20 吋）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>煞車</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>V 煞前後</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>V 煞前後</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>後機械碟 + 前 V</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>30 kg 整車加小孩下坡，V 煞不過 JIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>車架</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>公版鋁／鋼、無內走線</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>公版</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>通過幼児二人同乗基準之公版（BAA／SG）、両立スタンド、把手鎖</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>仍是零開模公版</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>電池訂閱層級</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>180／252Wh</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>144／202Wh</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>360Wh（更換週期抓 36 月）</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>電池在訂閱側切換，不動出廠價</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>目標市場</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>台北、阿姆斯特丹、柏林等平地都會</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>東京 23 區、大阪</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>橫濱、神戶、長崎；日本載童家庭</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>長坡（&gt;10 分鐘連續爬升）不保證</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>B. 材料增額與出廠價（RMB，對配置 C）</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>平地版</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>日本平地版</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>坡地載童版</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>依據</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>配置 C 材料（不含電池、充電器）</t>
+        </is>
+      </c>
+      <c r="B17" s="26">
+        <f>入手價!B8</f>
+        <v>799.216</v>
+      </c>
+      <c r="C17" s="26">
+        <f>入手價!B8</f>
+        <v>799.216</v>
+      </c>
+      <c r="D17" s="26">
+        <f>入手價!B8</f>
+        <v>799.216</v>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>入手價表</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>扭力感測淨增額</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="26">
+        <f>假設!$B$14</f>
+        <v>160.0</v>
+      </c>
+      <c r="D18" s="26">
+        <f>假設!$B$14</f>
+        <v>160.0</v>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>V3 分頁 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>日本非 BOM 增額（認定／PSE／說明書／OTP）</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="26">
+        <f>假設!$B$15</f>
+        <v>7.3</v>
+      </c>
+      <c r="D19" s="26">
+        <f>假設!$B$15</f>
+        <v>7.3</v>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>V3 分頁 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>馬達升級 40–45 N·m 級</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>假設：商品化 45 N·m 齒輪輪轂 RMB 280–300 vs 205</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>後機械碟煞（含碟煞座）</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>V3 分頁 2：機械碟 vs V 煞差 54</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>子乗せ車架強度與両立スタンド、把手鎖</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>假設：車架 +60、支撐與配件 +30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>20 吋輪組差額</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>20 吋成輪較 26 吋便宜</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>型式認定 + 子乗せ檢測攤提</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>¥2–3M ÷ 2 萬台 ≈ ¥120 ≈ RMB 5–8</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>材料合計（RMB）</t>
+        </is>
+      </c>
+      <c r="B25" s="24">
+        <f>B17+SUM(B18:B24)</f>
+        <v>799.216</v>
+      </c>
+      <c r="C25" s="24">
+        <f>C17+SUM(C18:C24)</f>
+        <v>966.5160000000001</v>
+      </c>
+      <c r="D25" s="24">
+        <f>D17+SUM(D18:D24)</f>
+        <v>1188.516</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>出廠價 @ODM 13%（RMB，不含電池）</t>
+        </is>
+      </c>
+      <c r="B26" s="13">
+        <f>(B25+假設!$B$7)/(1-假設!$B$8)</f>
+        <v>943.9264367816093</v>
+      </c>
+      <c r="C26" s="13">
+        <f>(C25+假設!$B$7)/(1-假設!$B$8)</f>
+        <v>1136.225287356322</v>
+      </c>
+      <c r="D26" s="13">
+        <f>(D25+假設!$B$7)/(1-假設!$B$8)</f>
+        <v>1391.3977011494253</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>出廠價 @ODM 18%（RMB）</t>
+        </is>
+      </c>
+      <c r="B27" s="12">
+        <f>(B25+假設!$B$7)/(1-假設!$B$9)</f>
+        <v>1001.4829268292682</v>
+      </c>
+      <c r="C27" s="12">
+        <f>(C25+假設!$B$7)/(1-假設!$B$9)</f>
+        <v>1205.5073170731707</v>
+      </c>
+      <c r="D27" s="12">
+        <f>(D25+假設!$B$7)/(1-假設!$B$9)</f>
+        <v>1476.239024390244</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>出廠價 @13%（NT$）</t>
+        </is>
+      </c>
+      <c r="B28" s="12">
+        <f>B26*假設!$B$20</f>
+        <v>4285.426022988506</v>
+      </c>
+      <c r="C28" s="12">
+        <f>C26*假設!$B$20</f>
+        <v>5158.462804597702</v>
+      </c>
+      <c r="D28" s="12">
+        <f>D26*假設!$B$20</f>
+        <v>6316.945563218391</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>出廠價 @13%（JPY）</t>
+        </is>
+      </c>
+      <c r="B29" s="12">
+        <f>B26*假設!$B$21</f>
+        <v>22182.271264367817</v>
+      </c>
+      <c r="C29" s="12">
+        <f>C26*假設!$B$21</f>
+        <v>26701.29425287357</v>
+      </c>
+      <c r="D29" s="12">
+        <f>D26*假設!$B$21</f>
+        <v>32697.845977011493</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>對平地版出廠價之溢出</t>
+        </is>
+      </c>
+      <c r="B30" s="17">
+        <f>B26/$B$26-1</f>
+        <v>0.0</v>
+      </c>
+      <c r="C30" s="17">
+        <f>C26/$B$26-1</f>
+        <v>0.2037222850017537</v>
+      </c>
+      <c r="D30" s="17">
+        <f>D26/$B$26-1</f>
+        <v>0.4740531114834585</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>C. 各市場零售（含稅）與電池訂閱</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>平地版</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>日本平地版</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>坡地載童版</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>公式</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>歐洲 DTC 零售 €（台越製）</t>
+        </is>
+      </c>
+      <c r="B34" s="13">
+        <f>(B26/假設!$B$19*(1+假設!$B$25)+假設!$B$26)/(1-假設!$B$27)*(1+假設!$B$46)</f>
+        <v>184.25709506500309</v>
+      </c>
+      <c r="C34" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="12">
+        <f>(D26/假設!$B$19*(1+假設!$B$25)+假設!$B$26)/(1-假設!$B$27)*(1+假設!$B$46)</f>
+        <v>264.66168949143656</v>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>入手價表結構；坡地版在歐洲坡地城市亦適用</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>台灣 DTC 零售 NT$</t>
+        </is>
+      </c>
+      <c r="B35" s="13">
+        <f>(B28+150)/(1-假設!$B$30)*(1+假設!$B$31)</f>
+        <v>7164.9189602122015</v>
+      </c>
+      <c r="C35" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D35" s="12">
+        <f>(D28+150)/(1-假設!$B$30)*(1+假設!$B$31)</f>
+        <v>10446.604371352785</v>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>台灣坡地（北投、基隆）可用坡地版</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>日本 PB 通路零售 ¥（税込）</t>
+        </is>
+      </c>
+      <c r="B36" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C36" s="13">
+        <f>((C29*(1+假設!$B$32)+假設!$B$33+假設!$B$34+假設!$B$35+假設!$B$36)-假設!$B$37)/(1-假設!$B$38)*(1+假設!$B$41)</f>
+        <v>48666.11517898195</v>
+      </c>
+      <c r="D36" s="13">
+        <f>((D29*(1+假設!$B$32)+假設!$B$33+假設!$B$34+假設!$B$35+假設!$B$36)-假設!$B$37)/(1-假設!$B$38)*(1+假設!$B$41)</f>
+        <v>58466.193996715934</v>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>V3 分頁 8 情境 3；載童版不含兒童座椅</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>日本 BESV 通路零售 ¥（15% + 22%）</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C37" s="12">
+        <f>(C29*(1+假設!$B$32)+假設!$B$33+假設!$B$34+假設!$B$35+假設!$B$36)/(1-假設!$B$39)/(1-假設!$B$40)*(1+假設!$B$41)</f>
+        <v>57188.96021913629</v>
+      </c>
+      <c r="D37" s="12">
+        <f>(D29*(1+假設!$B$32)+假設!$B$33+假設!$B$34+假設!$B$35+假設!$B$36)/(1-假設!$B$39)/(1-假設!$B$40)*(1+假設!$B$41)</f>
+        <v>67535.9514294135</v>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>V3 分頁 8 情境 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>電池訂閱月費（建議定價）</t>
+        </is>
+      </c>
+      <c r="B38" s="30" t="str">
+        <f>"€"&amp;TEXT(電池訂閱費!C19,"0.0")&amp;" / NT$"&amp;TEXT(電池訂閱費!C40,"#,##0")</f>
+        <v>€9.9 / NT$299</v>
+      </c>
+      <c r="C38" s="30" t="str">
+        <f>"¥"&amp;TEXT(電池訂閱費!C61,"#,##0")</f>
+        <v>¥1,280</v>
+      </c>
+      <c r="D38" s="30" t="str">
+        <f>"¥"&amp;TEXT(電池訂閱費!D61,"#,##0")</f>
+        <v>¥1,680</v>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>電池訂閱費表</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>日本對照（税込）</t>
+        </is>
+      </c>
+      <c r="B39" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Cainz PB ¥59,800／Panasonic ビビ EYX ¥89,800</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Panasonic Gyutto ¥170,000／Yamaha PAS Kiss ¥187,000</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>V3 分頁 8 C 段</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>D. 物理檢核：輪端扭矩、踏頻與騎士出力（藍字可改）</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>參數</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr"/>
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>重力加速度 g</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>m/s²</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>滾動阻力係數 Crr</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>盡調報告假設</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>空氣阻力（低速，N）</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>8–10 km/h 時約 2 N</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>26 吋輪半徑（m）</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>700c 亦約 0.33–0.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>20 吋輪半徑（m）</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="E47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>坡地檢核車速（km/h）</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>日本 10 km/h 以下適用 2:1 上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>日本騎士最低出力占比</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>助力比 1:2 → 騎士 ≥ 1/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>商品化輪轂輪端扭矩上限（N·m）</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>Bafang RM G010 級</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>45 N·m 級輪轂上限（N·m）</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="E51" s="11" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>情境</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>總重 kg</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>坡度</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>輪端扭矩需求 26 吋（N·m）</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>輪端扭矩需求 20 吋（N·m）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>平地通勤</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C54" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D54" s="32">
+        <f>(B54*$B$43*(C54+$B$44)+$B$45)*$B$46</f>
+        <v>28.500780000000006</v>
+      </c>
+      <c r="E54" s="32">
+        <f>(B54*$B$43*(C54+$B$44)+$B$45)*$B$47</f>
+        <v>21.936964000000003</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>平地通勤</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D55" s="32">
+        <f>(B55*$B$43*(C55+$B$44)+$B$45)*$B$46</f>
+        <v>34.97538</v>
+      </c>
+      <c r="E55" s="32">
+        <f>(B55*$B$43*(C55+$B$44)+$B$45)*$B$47</f>
+        <v>26.920444</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>載童</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>125</v>
+      </c>
+      <c r="C56" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D56" s="32">
+        <f>(B56*$B$43*(C56+$B$44)+$B$45)*$B$46</f>
+        <v>35.460975000000005</v>
+      </c>
+      <c r="E56" s="32">
+        <f>(B56*$B$43*(C56+$B$44)+$B$45)*$B$47</f>
+        <v>27.294205</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>載童</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>125</v>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D57" s="32">
+        <f>(B57*$B$43*(C57+$B$44)+$B$45)*$B$46</f>
+        <v>43.55422500000001</v>
+      </c>
+      <c r="E57" s="32">
+        <f>(B57*$B$43*(C57+$B$44)+$B$45)*$B$47</f>
+        <v>33.523555</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>判定：商品化 32 N·m 在 26 吋只夠 100 kg／8%；載童 125 kg／10% 需 45 N·m 級或改 20 吋</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>日本 2:1 下騎士出力（載童 125 kg、8% 坡、8 km/h）</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>26 吋 44/16</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>26 吋 38/18</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>20 吋 42/18</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>總功率需求 W</t>
+        </is>
+      </c>
+      <c r="B61" s="12">
+        <f>(B56*$B$43*(C56+$B$44)+$B$45)*$B$48/3.6</f>
+        <v>238.79444444444445</v>
+      </c>
+      <c r="C61" s="12">
+        <f>(B56*$B$43*(C56+$B$44)+$B$45)*$B$48/3.6</f>
+        <v>238.79444444444445</v>
+      </c>
+      <c r="D61" s="12">
+        <f>(B56*$B$43*(C56+$B$44)+$B$45)*$B$48/3.6</f>
+        <v>238.79444444444445</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>騎士出力 W（≥ 1/3）</t>
+        </is>
+      </c>
+      <c r="B62" s="12">
+        <f>B61*$B$49</f>
+        <v>79.59018833333333</v>
+      </c>
+      <c r="C62" s="12">
+        <f>C61*$B$49</f>
+        <v>79.59018833333333</v>
+      </c>
+      <c r="D62" s="12">
+        <f>D61*$B$49</f>
+        <v>79.59018833333333</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>輪周長 m</t>
+        </is>
+      </c>
+      <c r="B63" s="19">
+        <f>2*PI()*$B$46</f>
+        <v>2.0734511513692637</v>
+      </c>
+      <c r="C63" s="19">
+        <f>2*PI()*$B$46</f>
+        <v>2.0734511513692637</v>
+      </c>
+      <c r="D63" s="19">
+        <f>2*PI()*$B$47</f>
+        <v>1.595929068023615</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>齒比</t>
+        </is>
+      </c>
+      <c r="B64" s="19">
+        <f>44/16</f>
+        <v>2.75</v>
+      </c>
+      <c r="C64" s="19">
+        <f>38/18</f>
+        <v>2.111111111111111</v>
+      </c>
+      <c r="D64" s="19">
+        <f>42/18</f>
+        <v>2.3333333333333335</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>8 km/h 踏頻 rpm</t>
+        </is>
+      </c>
+      <c r="B65" s="15">
+        <f>$B$48*1000/60/B63/B64</f>
+        <v>23.383646367955237</v>
+      </c>
+      <c r="C65" s="15">
+        <f>$B$48*1000/60/C63/C64</f>
+        <v>30.460276189836424</v>
+      </c>
+      <c r="D65" s="15">
+        <f>$B$48*1000/60/D63/D64</f>
+        <v>35.805386522361154</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="16" t="inlineStr">
+        <is>
+          <t>騎士曲柄扭矩 N·m</t>
+        </is>
+      </c>
+      <c r="B66" s="23">
+        <f>B62/(B65*2*PI()/60)</f>
+        <v>32.502643160625006</v>
+      </c>
+      <c r="C66" s="23">
+        <f>C62/(C65*2*PI()/60)</f>
+        <v>24.9515240425</v>
+      </c>
+      <c r="D66" s="23">
+        <f>D62/(D65*2*PI()/60)</f>
+        <v>21.2267032285</v>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>一般通勤者持續上限約 25–30 N·m；20 吋 42/18 落在可行區</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>70 rpm 巡航速度 km/h</t>
+        </is>
+      </c>
+      <c r="B67" s="15">
+        <f>70*B64*B63*60/1000</f>
+        <v>23.948360798314997</v>
+      </c>
+      <c r="C67" s="15">
+        <f>70*C64*C63*60/1000</f>
+        <v>18.384600208807466</v>
+      </c>
+      <c r="D67" s="15">
+        <f>70*D64*D63*60/1000</f>
+        <v>15.640104866631425</v>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>日本媽媽車巡航 15–18 km/h</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>五年財務計畫（達方視角，NT$ 百萬）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>硬體以出廠價加達方毛利賣給通路；電池訂閱由達方（或 SPV）持有資產並收月費。藍字為量與比率假設。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>A. 量與組合假設</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>整車出貨量（台）</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>80000</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>110000</v>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>保守：原提案 Y5 45 萬台被盡調否決；30k 為出廠價達標門檻</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>歐洲平地版占比</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>日本平地版占比</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>日本載童版占比</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>台灣／其他平地版占比</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="11" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>電池訂閱附加率（未買斷比例）</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>提供買斷選項；假設 15% 買斷</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>訂戶年留存率</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>平均壽命 36 月 ≈ 年留存 75–80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>達方硬體毛利率（對出廠價加成）</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>品牌／整合／保固；8/28 門檻 ≥ 15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>B. 單價（NT$／台或／戶，連動模型）</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>歐洲平地</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>日本平地</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>日本載童</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>台灣平地</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>加權</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>出廠價（NT$）</t>
+        </is>
+      </c>
+      <c r="B17" s="26">
+        <f>三變體!B28</f>
+        <v>4285.426022988506</v>
+      </c>
+      <c r="C17" s="26">
+        <f>三變體!C28</f>
+        <v>5158.462804597702</v>
+      </c>
+      <c r="D17" s="26">
+        <f>三變體!D28</f>
+        <v>6316.945563218391</v>
+      </c>
+      <c r="E17" s="26">
+        <f>三變體!B28</f>
+        <v>4285.426022988506</v>
+      </c>
+      <c r="F17" s="24">
+        <f>B17*$B$7+C17*$B$8+D17*$B$9+E17*$B$10</f>
+        <v>4686.354988505747</v>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>三變體表；加權以 2027 組合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>電池月費（NT$，含稅）</t>
+        </is>
+      </c>
+      <c r="B18" s="26">
+        <f>電池訂閱費!C19*假設!$B$19*假設!$B$20</f>
+        <v>485.4168000000001</v>
+      </c>
+      <c r="C18" s="26">
+        <f>電池訂閱費!C61/假設!$B$21*假設!$B$20</f>
+        <v>247.28510638297874</v>
+      </c>
+      <c r="D18" s="26">
+        <f>電池訂閱費!D61/假設!$B$21*假設!$B$20</f>
+        <v>324.56170212765954</v>
+      </c>
+      <c r="E18" s="26">
+        <f>電池訂閱費!C40</f>
+        <v>299.0</v>
+      </c>
+      <c r="F18" s="24">
+        <f>B18*$B$7+C18*$B$8+D18*$B$9+E18*$B$10</f>
+        <v>385.9671234042554</v>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>€9.9／¥1,280／¥1,680／NT$299</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>月費淨額係數（除 VAT／消費稅）</t>
+        </is>
+      </c>
+      <c r="B19" s="19">
+        <f>1/(1+假設!$B$46)</f>
+        <v>0.8403361344537815</v>
+      </c>
+      <c r="C19" s="19">
+        <f>1/(1+假設!$B$41)</f>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="D19" s="19">
+        <f>1/(1+假設!$B$41)</f>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="E19" s="19">
+        <f>1/(1+假設!$B$31)</f>
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="F19" s="19">
+        <f>B19*$B$7+C19*$B$8+D19*$B$9+E19*$B$10</f>
+        <v>0.883371530430354</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>每戶每月現金成本（NT$，③④⑤⑥ + 呆帳金流）</t>
+        </is>
+      </c>
+      <c r="B20" s="12">
+        <f>(電池訂閱費!C12+電池訂閱費!C13+電池訂閱費!C19/(1+假設!$B$46)*(假設!$B$47+假設!$B$48))*假設!$B$19*假設!$B$20</f>
+        <v>186.4749060714286</v>
+      </c>
+      <c r="C20" s="12">
+        <f>(電池訂閱費!C54+電池訂閱費!C55+電池訂閱費!C61/(1+假設!$B$41)*(假設!$B$75+假設!$B$76))/假設!$B$21*假設!$B$20</f>
+        <v>103.66370200123791</v>
+      </c>
+      <c r="D20" s="12">
+        <f>(電池訂閱費!D54+電池訂閱費!D55+電池訂閱費!D61/(1+假設!$B$41)*(假設!$B$75+假設!$B$76))/假設!$B$21*假設!$B$20</f>
+        <v>120.33410397524177</v>
+      </c>
+      <c r="E20" s="12">
+        <f>電池訂閱費!C33+電池訂閱費!C34+電池訂閱費!C40/(1+假設!$B$31)*(假設!$B$61+假設!$B$62)</f>
+        <v>110.22742261904762</v>
+      </c>
+      <c r="F20" s="24">
+        <f>B20*$B$7+C20*$B$8+D20*$B$9+E20*$B$10</f>
+        <v>148.38249639677565</v>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>更換準備 + 失竊／客服／物流 + 呆帳金流；資產與 CAC 另列</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>每戶電池 + 充電器資產（NT$）</t>
+        </is>
+      </c>
+      <c r="B21" s="26">
+        <f>電池訂閱費!C9*假設!$B$19*假設!$B$20</f>
+        <v>2007.0341199999998</v>
+      </c>
+      <c r="C21" s="26">
+        <f>電池訂閱費!C51/假設!$B$21*假設!$B$20</f>
+        <v>1658.1907869685108</v>
+      </c>
+      <c r="D21" s="26">
+        <f>電池訂閱費!D51/假設!$B$21*假設!$B$20</f>
+        <v>2239.1855556085106</v>
+      </c>
+      <c r="E21" s="26">
+        <f>電池訂閱費!C30</f>
+        <v>1808.4019999999998</v>
+      </c>
+      <c r="F21" s="24">
+        <f>B21*$B$7+C21*$B$8+D21*$B$9+E21*$B$10</f>
+        <v>1932.3740683273531</v>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>資本支出；4 年折舊</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>每戶 CAC（NT$）</t>
+        </is>
+      </c>
+      <c r="B22" s="26">
+        <f>假設!$B$55*假設!$B$19*假設!$B$20</f>
+        <v>1470.96</v>
+      </c>
+      <c r="C22" s="26">
+        <f>假設!$B$83/假設!$B$21*假設!$B$20</f>
+        <v>579.5744680851064</v>
+      </c>
+      <c r="D22" s="26">
+        <f>假設!$B$83/假設!$B$21*假設!$B$20</f>
+        <v>579.5744680851064</v>
+      </c>
+      <c r="E22" s="26">
+        <f>假設!$B$69</f>
+        <v>800.0</v>
+      </c>
+      <c r="F22" s="24">
+        <f>B22*$B$7+C22*$B$8+D22*$B$9+E22*$B$10</f>
+        <v>1069.352340425532</v>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>隨車成交</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>C. 營運費用假設（NT$ 百萬／年）</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>三電 RD（韌體、控制器、電池包）</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>8/28：RD NT$3–5M 上限起步</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>APP／雲端／資料團隊</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>BOM 報告：完整 IoT 平台 NT$12M；本案 BLE + SoH 較輕</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>認證與模具（EN 15194／UN38.3／日本型式認定 ×3／PSE）</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>US$130k + ¥2–3M + 模具</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>翻新中心與逆物流建置（歐、日各一）</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>含治具、危險品倉儲</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>行銷與通路（佔硬體營收）</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>比率；DTC 與 B2B2C 混合</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>管理與其他（佔總營收）</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>比率</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>D. 損益與現金流（NT$ 百萬）</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>公式</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>新增訂戶（戶）</t>
+        </is>
+      </c>
+      <c r="B35" s="12">
+        <f>B6*B11</f>
+        <v>6800.0</v>
+      </c>
+      <c r="C35" s="12">
+        <f>C6*C11</f>
+        <v>21250.0</v>
+      </c>
+      <c r="D35" s="12">
+        <f>D6*D11</f>
+        <v>42500.0</v>
+      </c>
+      <c r="E35" s="12">
+        <f>E6*E11</f>
+        <v>68000.0</v>
+      </c>
+      <c r="F35" s="12">
+        <f>F6*F11</f>
+        <v>93500.0</v>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>出貨 × 附加率</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>期末在訂戶（戶）</t>
+        </is>
+      </c>
+      <c r="B36" s="24">
+        <f>B35</f>
+        <v>6800.0</v>
+      </c>
+      <c r="C36" s="24">
+        <f>B36*C12+C35</f>
+        <v>26690.0</v>
+      </c>
+      <c r="D36" s="24">
+        <f>C36*D12+D35</f>
+        <v>63852.0</v>
+      </c>
+      <c r="E36" s="24">
+        <f>D36*E12+E35</f>
+        <v>119081.6</v>
+      </c>
+      <c r="F36" s="24">
+        <f>E36*F12+F35</f>
+        <v>188765.28000000003</v>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>上期 × 留存 + 新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>平均在訂戶（戶）</t>
+        </is>
+      </c>
+      <c r="B37" s="12">
+        <f>B36/2</f>
+        <v>3400.0</v>
+      </c>
+      <c r="C37" s="12">
+        <f>(B36+C36)/2</f>
+        <v>16745.0</v>
+      </c>
+      <c r="D37" s="12">
+        <f>(C36+D36)/2</f>
+        <v>45271.0</v>
+      </c>
+      <c r="E37" s="12">
+        <f>(D36+E36)/2</f>
+        <v>91466.8</v>
+      </c>
+      <c r="F37" s="12">
+        <f>(E36+F36)/2</f>
+        <v>153923.44</v>
+      </c>
+      <c r="G37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>硬體營收</t>
+        </is>
+      </c>
+      <c r="B38" s="18">
+        <f>B6*$F$17*(1+B13)/1000000</f>
+        <v>44.98900788965517</v>
+      </c>
+      <c r="C38" s="18">
+        <f>C6*$F$17*(1+C13)/1000000</f>
+        <v>140.5906496551724</v>
+      </c>
+      <c r="D38" s="18">
+        <f>D6*$F$17*(1+D13)/1000000</f>
+        <v>281.1812993103448</v>
+      </c>
+      <c r="E38" s="18">
+        <f>E6*$F$17*(1+E13)/1000000</f>
+        <v>449.89007889655176</v>
+      </c>
+      <c r="F38" s="18">
+        <f>F6*$F$17*(1+F13)/1000000</f>
+        <v>618.5988584827586</v>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>出貨 × 出廠價 × (1 + 達方毛利)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>硬體成本</t>
+        </is>
+      </c>
+      <c r="B39" s="15">
+        <f>B6*$F$17/1000000</f>
+        <v>37.49083990804598</v>
+      </c>
+      <c r="C39" s="15">
+        <f>C6*$F$17/1000000</f>
+        <v>117.15887471264368</v>
+      </c>
+      <c r="D39" s="15">
+        <f>D6*$F$17/1000000</f>
+        <v>234.31774942528736</v>
+      </c>
+      <c r="E39" s="15">
+        <f>E6*$F$17/1000000</f>
+        <v>374.9083990804598</v>
+      </c>
+      <c r="F39" s="15">
+        <f>F6*$F$17/1000000</f>
+        <v>515.4990487356322</v>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>以出廠價採購</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>訂閱營收（淨額）</t>
+        </is>
+      </c>
+      <c r="B40" s="18">
+        <f>B37*$F$18*$F$19*12/1000000</f>
+        <v>13.91085663469467</v>
+      </c>
+      <c r="C40" s="18">
+        <f>C37*$F$18*$F$19*12/1000000</f>
+        <v>68.51096892587125</v>
+      </c>
+      <c r="D40" s="18">
+        <f>D37*$F$18*$F$19*12/1000000</f>
+        <v>185.22305609095955</v>
+      </c>
+      <c r="E40" s="18">
+        <f>E37*$F$18*$F$19*12/1000000</f>
+        <v>374.229865186556</v>
+      </c>
+      <c r="F40" s="18">
+        <f>F37*$F$18*$F$19*12/1000000</f>
+        <v>629.7667372232432</v>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>平均戶 × 月費淨額 × 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>訂閱現金成本</t>
+        </is>
+      </c>
+      <c r="B41" s="15">
+        <f>B37*$F$20*12/1000000</f>
+        <v>6.054005852988446</v>
+      </c>
+      <c r="C41" s="15">
+        <f>C37*$F$20*12/1000000</f>
+        <v>29.815978825968102</v>
+      </c>
+      <c r="D41" s="15">
+        <f>D37*$F$20*12/1000000</f>
+        <v>80.60908793254116</v>
+      </c>
+      <c r="E41" s="15">
+        <f>E37*$F$20*12/1000000</f>
+        <v>162.86486545709516</v>
+      </c>
+      <c r="F41" s="15">
+        <f>F37*$F$20*12/1000000</f>
+        <v>274.0745313741518</v>
+      </c>
+      <c r="G41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>訂閱 CAC</t>
+        </is>
+      </c>
+      <c r="B42" s="15">
+        <f>B35*$F$22/1000000</f>
+        <v>7.271595914893618</v>
+      </c>
+      <c r="C42" s="15">
+        <f>C35*$F$22/1000000</f>
+        <v>22.723737234042556</v>
+      </c>
+      <c r="D42" s="15">
+        <f>D35*$F$22/1000000</f>
+        <v>45.44747446808511</v>
+      </c>
+      <c r="E42" s="15">
+        <f>E35*$F$22/1000000</f>
+        <v>72.71595914893618</v>
+      </c>
+      <c r="F42" s="15">
+        <f>F35*$F$22/1000000</f>
+        <v>99.98444382978724</v>
+      </c>
+      <c r="G42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>電池資產折舊（4 年）</t>
+        </is>
+      </c>
+      <c r="B43" s="15">
+        <f>B35*$F$21/4/1000000</f>
+        <v>3.2850359161565</v>
+      </c>
+      <c r="C43" s="15">
+        <f>B35*$F$21/4/1000000+C35*$F$21/4/1000000</f>
+        <v>13.550773154145565</v>
+      </c>
+      <c r="D43" s="15">
+        <f>B35*$F$21/4/1000000+C35*$F$21/4/1000000+D35*$F$21/4/1000000</f>
+        <v>34.082247630123696</v>
+      </c>
+      <c r="E43" s="15">
+        <f>B35*$F$21/4/1000000+C35*$F$21/4/1000000+D35*$F$21/4/1000000+E35*$F$21/4/1000000</f>
+        <v>66.9326067916887</v>
+      </c>
+      <c r="F43" s="15">
+        <f>C35*$F$21/4/1000000+D35*$F$21/4/1000000+E35*$F$21/4/1000000+F35*$F$21/4/1000000</f>
+        <v>108.81681472268409</v>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>新增訂戶資產 ÷ 4，攤 4 年</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>總營收</t>
+        </is>
+      </c>
+      <c r="B44" s="23">
+        <f>B38+B40</f>
+        <v>58.89986452434984</v>
+      </c>
+      <c r="C44" s="23">
+        <f>C38+C40</f>
+        <v>209.10161858104365</v>
+      </c>
+      <c r="D44" s="23">
+        <f>D38+D40</f>
+        <v>466.4043554013043</v>
+      </c>
+      <c r="E44" s="23">
+        <f>E38+E40</f>
+        <v>824.1199440831078</v>
+      </c>
+      <c r="F44" s="23">
+        <f>F38+F40</f>
+        <v>1248.3655957060018</v>
+      </c>
+      <c r="G44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>毛利（硬體 + 訂閱，含折舊）</t>
+        </is>
+      </c>
+      <c r="B45" s="18">
+        <f>B38-B39+B40-B41-B42-B43</f>
+        <v>4.798386932265295</v>
+      </c>
+      <c r="C45" s="18">
+        <f>C38-C39+C40-C41-C42-C43</f>
+        <v>25.852254654243744</v>
+      </c>
+      <c r="D45" s="18">
+        <f>D38-D39+D40-D41-D42-D43</f>
+        <v>71.94779594526699</v>
+      </c>
+      <c r="E45" s="18">
+        <f>E38-E39+E40-E41-E42-E43</f>
+        <v>146.69811360492795</v>
+      </c>
+      <c r="F45" s="18">
+        <f>F38-F39+F40-F41-F42-F43</f>
+        <v>249.99075704374658</v>
+      </c>
+      <c r="G45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>毛利率</t>
+        </is>
+      </c>
+      <c r="B46" s="17">
+        <f>IF(B44&gt;0,B45/B44,0)</f>
+        <v>0.08146685855757088</v>
+      </c>
+      <c r="C46" s="17">
+        <f>IF(C44&gt;0,C45/C44,0)</f>
+        <v>0.12363488541923419</v>
+      </c>
+      <c r="D46" s="17">
+        <f>IF(D44&gt;0,D45/D44,0)</f>
+        <v>0.15426055763000232</v>
+      </c>
+      <c r="E46" s="17">
+        <f>IF(E44&gt;0,E45/E44,0)</f>
+        <v>0.1780057801757729</v>
+      </c>
+      <c r="F46" s="17">
+        <f>IF(F44&gt;0,F45/F44,0)</f>
+        <v>0.2002544430122384</v>
+      </c>
+      <c r="G46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>RD + APP + 認證 + 翻新建置</t>
+        </is>
+      </c>
+      <c r="B47" s="15">
+        <f>B26+B27+B28+B29</f>
+        <v>18.0</v>
+      </c>
+      <c r="C47" s="15">
+        <f>C26+C27+C28+C29</f>
+        <v>27.0</v>
+      </c>
+      <c r="D47" s="15">
+        <f>D26+D27+D28+D29</f>
+        <v>24.0</v>
+      </c>
+      <c r="E47" s="15">
+        <f>E26+E27+E28+E29</f>
+        <v>22.0</v>
+      </c>
+      <c r="F47" s="15">
+        <f>F26+F27+F28+F29</f>
+        <v>22.0</v>
+      </c>
+      <c r="G47" s="6" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>行銷與通路</t>
+        </is>
+      </c>
+      <c r="B48" s="15">
+        <f>B38*B30</f>
+        <v>3.5991206311724135</v>
+      </c>
+      <c r="C48" s="15">
+        <f>C38*C30</f>
+        <v>8.435438979310344</v>
+      </c>
+      <c r="D48" s="15">
+        <f>D38*D30</f>
+        <v>14.05906496551724</v>
+      </c>
+      <c r="E48" s="15">
+        <f>E38*E30</f>
+        <v>22.49450394482759</v>
+      </c>
+      <c r="F48" s="15">
+        <f>F38*F30</f>
+        <v>30.929942924137933</v>
+      </c>
+      <c r="G48" s="6" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>管理與其他</t>
+        </is>
+      </c>
+      <c r="B49" s="15">
+        <f>B44*B31</f>
+        <v>2.3559945809739937</v>
+      </c>
+      <c r="C49" s="15">
+        <f>C44*C31</f>
+        <v>6.273048557431309</v>
+      </c>
+      <c r="D49" s="15">
+        <f>D44*D31</f>
+        <v>13.992130662039129</v>
+      </c>
+      <c r="E49" s="15">
+        <f>E44*E31</f>
+        <v>24.723598322493235</v>
+      </c>
+      <c r="F49" s="15">
+        <f>F44*F31</f>
+        <v>37.450967871180055</v>
+      </c>
+      <c r="G49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B50" s="23">
+        <f>B45-B47-B48-B49</f>
+        <v>-19.156728279881115</v>
+      </c>
+      <c r="C50" s="23">
+        <f>C45-C47-C48-C49</f>
+        <v>-15.85623288249791</v>
+      </c>
+      <c r="D50" s="23">
+        <f>D45-D47-D48-D49</f>
+        <v>19.89660031771062</v>
+      </c>
+      <c r="E50" s="23">
+        <f>E45-E47-E48-E49</f>
+        <v>77.48001133760714</v>
+      </c>
+      <c r="F50" s="23">
+        <f>F45-F47-F48-F49</f>
+        <v>159.6098462484286</v>
+      </c>
+      <c r="G50" s="6" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>EBIT 率</t>
+        </is>
+      </c>
+      <c r="B51" s="17">
+        <f>IF(B44&gt;0,B50/B44,0)</f>
+        <v>-0.3252423148097653</v>
+      </c>
+      <c r="C51" s="17">
+        <f>IF(C44&gt;0,C50/C44,0)</f>
+        <v>-0.07583027329055489</v>
+      </c>
+      <c r="D51" s="17">
+        <f>IF(D44&gt;0,D50/D44,0)</f>
+        <v>0.04265955085387477</v>
+      </c>
+      <c r="E51" s="17">
+        <f>IF(E44&gt;0,E50/E44,0)</f>
+        <v>0.09401545478165702</v>
+      </c>
+      <c r="F51" s="17">
+        <f>IF(F44&gt;0,F50/F44,0)</f>
+        <v>0.12785505047354553</v>
+      </c>
+      <c r="G51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>電池資本支出</t>
+        </is>
+      </c>
+      <c r="B52" s="15">
+        <f>B35*$F$21/1000000</f>
+        <v>13.140143664626</v>
+      </c>
+      <c r="C52" s="15">
+        <f>C35*$F$21/1000000</f>
+        <v>41.06294895195626</v>
+      </c>
+      <c r="D52" s="15">
+        <f>D35*$F$21/1000000</f>
+        <v>82.12589790391252</v>
+      </c>
+      <c r="E52" s="15">
+        <f>E35*$F$21/1000000</f>
+        <v>131.40143664626</v>
+      </c>
+      <c r="F52" s="15">
+        <f>F35*$F$21/1000000</f>
+        <v>180.67697538860753</v>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>新增訂戶 × 每戶資產</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>營運現金流（EBIT + 折舊 − 電池資本支出）</t>
+        </is>
+      </c>
+      <c r="B53" s="18">
+        <f>B50+B43-B52</f>
+        <v>-29.011836028350615</v>
+      </c>
+      <c r="C53" s="18">
+        <f>C50+C43-C52</f>
+        <v>-43.368408680308605</v>
+      </c>
+      <c r="D53" s="18">
+        <f>D50+D43-D52</f>
+        <v>-28.1470499560782</v>
+      </c>
+      <c r="E53" s="18">
+        <f>E50+E43-E52</f>
+        <v>13.011181483035813</v>
+      </c>
+      <c r="F53" s="18">
+        <f>F50+F43-F52</f>
+        <v>87.74968558250518</v>
+      </c>
+      <c r="G53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>累計現金流</t>
+        </is>
+      </c>
+      <c r="B54" s="23">
+        <f>B53</f>
+        <v>-29.011836028350615</v>
+      </c>
+      <c r="C54" s="23">
+        <f>B54+C53</f>
+        <v>-72.38024470865922</v>
+      </c>
+      <c r="D54" s="23">
+        <f>C54+D53</f>
+        <v>-100.52729466473741</v>
+      </c>
+      <c r="E54" s="23">
+        <f>D54+E53</f>
+        <v>-87.5161131817016</v>
+      </c>
+      <c r="F54" s="23">
+        <f>E54+F53</f>
+        <v>0.2335724008035811</v>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>最低點 = 資金需求峰值（未含營運資金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>電池車隊資產（毛額，期末）</t>
+        </is>
+      </c>
+      <c r="B55" s="15">
+        <f>B52</f>
+        <v>13.140143664626</v>
+      </c>
+      <c r="C55" s="15">
+        <f>B52+C52</f>
+        <v>54.20309261658226</v>
+      </c>
+      <c r="D55" s="15">
+        <f>B52+C52+D52</f>
+        <v>136.32899052049478</v>
+      </c>
+      <c r="E55" s="15">
+        <f>B52+C52+D52+E52</f>
+        <v>267.7304271667548</v>
+      </c>
+      <c r="F55" s="15">
+        <f>B52+C52+D52+E52+F52</f>
+        <v>448.4074025553623</v>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>可由 SPV／租賃夥伴持有</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>資金需求峰值（累計現金流最低點）</t>
+        </is>
+      </c>
+      <c r="B56" s="23">
+        <f>-MIN(B54:F54)</f>
+        <v>100.52729466473741</v>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>若電池資產由 SPV 持有，達方峰值 ≈ 此值 − 電池資本支出累計</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>若 SPV 持有電池：達方累計現金流最低點</t>
+        </is>
+      </c>
+      <c r="B57" s="18">
+        <f>MIN(B54+B55,C54+C55,D54+D55,E54+E55,F54+F55)</f>
+        <v>-18.17715209207696</v>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>SPV 融資成本未計</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/三電系統開發/V3補充_電池充電器拆分訂閱模型_20260921.xlsx
+++ b/三電系統開發/V3補充_電池充電器拆分訂閱模型_20260921.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日本付款路徑" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="三變體" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="五年財務" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="兩條路對照" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -138,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -227,6 +228,12 @@
     </xf>
     <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8484,4 +8491,1265 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>兩條路五年對照與決策門檻：合規電池平台 + OEM 服務（C1） vs 低價整車 + 電池訂閱（B2C）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>C1 參數取自 V4 分頁 11；B2C 連動五年財務分頁並以量級倍數做情境。NT$ 百萬除非另註。藍字可改。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>A. C1 假設（V4 分頁 11）</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>參數</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>來源</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>三電成本 €/台</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>RMB 595 ÷ 10.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>賣 OEM 毛利率</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 常見 20–30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>服務合約 €/台/年</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>護照、EPR、備品、SoH、回收；無公開價格</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>服務成本 €/台/年</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>系統、行政、備品攤提</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>在保年數（服務收費期）</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>備品義務 5 年</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>EUR/NTD</t>
+        </is>
+      </c>
+      <c r="B11" s="33">
+        <f>假設!$B$19*假設!$B$20</f>
+        <v>49.032000000000004</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>＝ RMB/EUR × NTD/RMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>C1 固定費用：合規系統與團隊（NT$M/年）</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>護照平台 €80–150k + EPR 27 國 + 團隊；假設</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>C1 建置一次性（NT$M，第一年）</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>系統與備品初始庫存</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>C1 第一年出貨占穩態比例</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>爬坡</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>C1 年出貨情境（台/年）</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>悲觀</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>基準</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>樂觀</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>三電白牌年出貨</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>歐洲中價位用八方／安乃達的品牌約 30–45 萬台/年（估）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>第 5 年在保台數</t>
+        </is>
+      </c>
+      <c r="B18" s="12">
+        <f>B17*$B$10</f>
+        <v>150000.0</v>
+      </c>
+      <c r="C18" s="12">
+        <f>C17*$B$10</f>
+        <v>300000.0</v>
+      </c>
+      <c r="D18" s="12">
+        <f>D17*$B$10</f>
+        <v>500000.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>第 5 年硬體毛利（NT$M）</t>
+        </is>
+      </c>
+      <c r="B19" s="15">
+        <f>B17*$B$6/(1-$B$7)*$B$7*$B$11/1000000</f>
+        <v>26.967600000000004</v>
+      </c>
+      <c r="C19" s="15">
+        <f>C17*$B$6/(1-$B$7)*$B$7*$B$11/1000000</f>
+        <v>53.93520000000001</v>
+      </c>
+      <c r="D19" s="15">
+        <f>D17*$B$6/(1-$B$7)*$B$7*$B$11/1000000</f>
+        <v>89.892</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>第 5 年服務毛利（NT$M）</t>
+        </is>
+      </c>
+      <c r="B20" s="15">
+        <f>B18*($B$8-$B$9)*$B$11/1000000</f>
+        <v>40.4514</v>
+      </c>
+      <c r="C20" s="15">
+        <f>C18*($B$8-$B$9)*$B$11/1000000</f>
+        <v>80.9028</v>
+      </c>
+      <c r="D20" s="15">
+        <f>D18*($B$8-$B$9)*$B$11/1000000</f>
+        <v>134.838</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>第 5 年營收（NT$M）</t>
+        </is>
+      </c>
+      <c r="B21" s="15">
+        <f>(B17*$B$6/(1-$B$7)+B18*$B$8)*$B$11/1000000</f>
+        <v>181.4184</v>
+      </c>
+      <c r="C21" s="15">
+        <f>(C17*$B$6/(1-$B$7)+C18*$B$8)*$B$11/1000000</f>
+        <v>362.8368</v>
+      </c>
+      <c r="D21" s="15">
+        <f>(D17*$B$6/(1-$B$7)+D18*$B$8)*$B$11/1000000</f>
+        <v>604.728</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>第 5 年 EBIT（NT$M）</t>
+        </is>
+      </c>
+      <c r="B22" s="23">
+        <f>B19+B20-$B$12</f>
+        <v>42.41900000000001</v>
+      </c>
+      <c r="C22" s="23">
+        <f>C19+C20-$B$12</f>
+        <v>109.83800000000002</v>
+      </c>
+      <c r="D22" s="23">
+        <f>D19+D20-$B$12</f>
+        <v>199.73</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>五年累計 EBIT（NT$M，服務基數線性累積）</t>
+        </is>
+      </c>
+      <c r="B23" s="15">
+        <f>5*B19+B20*(1+2+3+4+5)/5-5*$B$12-$B$13</f>
+        <v>116.19220000000001</v>
+      </c>
+      <c r="C23" s="15">
+        <f>5*C19+C20*(1+2+3+4+5)/5-5*$B$12-$B$13</f>
+        <v>372.3844</v>
+      </c>
+      <c r="D23" s="15">
+        <f>5*D19+D20*(1+2+3+4+5)/5-5*$B$12-$B$13</f>
+        <v>713.9739999999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>資金需求峰值（NT$M）</t>
+        </is>
+      </c>
+      <c r="B24" s="18">
+        <f>MAX($B$13+$B$12-(B19+B20/5)*$B$14,0)</f>
+        <v>22.471059999999998</v>
+      </c>
+      <c r="C24" s="18">
+        <f>MAX($B$13+$B$12-(C19+C20/5)*$B$14,0)</f>
+        <v>4.942119999999996</v>
+      </c>
+      <c r="D24" s="18">
+        <f>MAX($B$13+$B$12-(D19+D20/5)*$B$14,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>第一年：建置 + 固定費用 − 首年毛利；零電池資產、零 CAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>B. B2C 情境（連動五年財務分頁，以量級倍數縮放）</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>悲觀</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>基準</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>樂觀</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>量級倍數（對五年財務基準 110k）</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>悲觀 40k、基準 110k、樂觀 250k（SAM 4.7M 的 1–5%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>第 5 年出貨（台）</t>
+        </is>
+      </c>
+      <c r="B29" s="12">
+        <f>B28*五年財務!F6</f>
+        <v>39600.0</v>
+      </c>
+      <c r="C29" s="12">
+        <f>C28*五年財務!F6</f>
+        <v>110000.0</v>
+      </c>
+      <c r="D29" s="12">
+        <f>D28*五年財務!F6</f>
+        <v>252999.99999999997</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>第 5 年營收（NT$M）</t>
+        </is>
+      </c>
+      <c r="B30" s="15">
+        <f>B28*五年財務!F44</f>
+        <v>449.41161445416066</v>
+      </c>
+      <c r="C30" s="15">
+        <f>C28*五年財務!F44</f>
+        <v>1248.3655957060018</v>
+      </c>
+      <c r="D30" s="15">
+        <f>D28*五年財務!F44</f>
+        <v>2871.240870123804</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>第 5 年 EBIT（NT$M）</t>
+        </is>
+      </c>
+      <c r="B31" s="23">
+        <f>B28*(五年財務!F45-五年財務!F48-五年財務!F49)-五年財務!F47</f>
+        <v>43.379544649434294</v>
+      </c>
+      <c r="C31" s="23">
+        <f>C28*(五年財務!F45-五年財務!F48-五年財務!F49)-五年財務!F47</f>
+        <v>159.6098462484286</v>
+      </c>
+      <c r="D31" s="23">
+        <f>D28*(五年財務!F45-五年財務!F48-五年財務!F49)-五年財務!F47</f>
+        <v>395.70264637138575</v>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>毛利與變動費用隨量縮放，RD／APP／認證／翻新建置固定</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>五年累計現金流（NT$M）</t>
+        </is>
+      </c>
+      <c r="B32" s="15">
+        <f>B28*(五年財務!F54+SUM(五年財務!B47:F47))-SUM(五年財務!B47:F47)</f>
+        <v>-72.23591393571071</v>
+      </c>
+      <c r="C32" s="15">
+        <f>C28*(五年財務!F54+SUM(五年財務!B47:F47))-SUM(五年財務!B47:F47)</f>
+        <v>0.2335724008035811</v>
+      </c>
+      <c r="D32" s="15">
+        <f>D28*(五年財務!F54+SUM(五年財務!B47:F47))-SUM(五年財務!B47:F47)</f>
+        <v>147.4372165218482</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>資金需求峰值（NT$M，自持電池）</t>
+        </is>
+      </c>
+      <c r="B33" s="18">
+        <f>B28*(五年財務!B56-SUM(五年財務!B47:D47))+SUM(五年財務!B47:D47)</f>
+        <v>80.34982607930547</v>
+      </c>
+      <c r="C33" s="18">
+        <f>C28*(五年財務!B56-SUM(五年財務!B47:D47))+SUM(五年財務!B47:D47)</f>
+        <v>100.52729466473741</v>
+      </c>
+      <c r="D33" s="18">
+        <f>D28*(五年財務!B56-SUM(五年財務!B47:D47))+SUM(五年財務!B47:D47)</f>
+        <v>141.51277772889603</v>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>近似：峰值中的電池資本與 CAC 隨量縮放，前三年固定費用不縮放</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>資金需求峰值（NT$M，SPV 持有電池）</t>
+        </is>
+      </c>
+      <c r="B34" s="15">
+        <f>MAX(B28*(-五年財務!B57-SUM(五年財務!B47:C47))+SUM(五年財務!B47:C47),0)</f>
+        <v>35.343774753147706</v>
+      </c>
+      <c r="C34" s="15">
+        <f>MAX(C28*(-五年財務!B57-SUM(五年財務!B47:C47))+SUM(五年財務!B47:C47),0)</f>
+        <v>18.17715209207696</v>
+      </c>
+      <c r="D34" s="15">
+        <f>MAX(D28*(-五年財務!B57-SUM(五年財務!B47:C47))+SUM(五年財務!B47:C47),0)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>第 5 年在訂戶（戶）</t>
+        </is>
+      </c>
+      <c r="B35" s="12">
+        <f>B28*五年財務!F36</f>
+        <v>67955.50080000001</v>
+      </c>
+      <c r="C35" s="12">
+        <f>C28*五年財務!F36</f>
+        <v>188765.28000000003</v>
+      </c>
+      <c r="D35" s="12">
+        <f>D28*五年財務!F36</f>
+        <v>434160.14400000003</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>C. 五年對照（基準情境）</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>面向</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>C1 合規電池平台 + OEM 服務</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>B2C 低價整車 + 電池訂閱</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr"/>
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>判讀</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>第 5 年營收（NT$M）</t>
+        </is>
+      </c>
+      <c r="B39" s="15">
+        <f>C21</f>
+        <v>362.8368</v>
+      </c>
+      <c r="C39" s="15">
+        <f>C30</f>
+        <v>1248.3655957060018</v>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>B2C 約為 C1 的 2.5–3 倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>第 5 年 EBIT（NT$M）</t>
+        </is>
+      </c>
+      <c r="B40" s="18">
+        <f>C22</f>
+        <v>109.83800000000002</v>
+      </c>
+      <c r="C40" s="18">
+        <f>C31</f>
+        <v>159.6098462484286</v>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>同一數量級</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>資金需求峰值（NT$M）</t>
+        </is>
+      </c>
+      <c r="B41" s="15">
+        <f>C24</f>
+        <v>4.942119999999996</v>
+      </c>
+      <c r="C41" s="15">
+        <f>C33</f>
+        <v>100.52729466473741</v>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>B2C 自持電池；SPV 時見 B 段</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>EBIT ÷ 峰值資金（倍）</t>
+        </is>
+      </c>
+      <c r="B42" s="19">
+        <f>IF(C24&gt;0,C22/C24,99)</f>
+        <v>22.224875154791896</v>
+      </c>
+      <c r="C42" s="19">
+        <f>C31/C33</f>
+        <v>1.5877264655408652</v>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>資本效率</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>悲觀情境第 5 年 EBIT（NT$M）</t>
+        </is>
+      </c>
+      <c r="B43" s="15">
+        <f>B22</f>
+        <v>42.41900000000001</v>
+      </c>
+      <c r="C43" s="15">
+        <f>B31</f>
+        <v>43.379544649434294</v>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>下檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>樂觀情境第 5 年 EBIT（NT$M）</t>
+        </is>
+      </c>
+      <c r="B44" s="15">
+        <f>D22</f>
+        <v>199.73</v>
+      </c>
+      <c r="C44" s="15">
+        <f>D31</f>
+        <v>395.70264637138575</v>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>上檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>要新建的能力</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>幾乎無：既有電池包業務延伸</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>C 端客服、催收、逆向物流、車隊管理、通路、品牌（2–3 年）</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>V4 分頁 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>護城河</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>車型級鎖定（認證 + 護照 + 備品），窗口 2027–2029</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>電池池 + 資料迴圈（RMB 186/台級），營運型</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>皆非技術型</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>最大單一風險</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>合規被 BMZ／Bafang 歐洲實體／橫向 EPR 業者商品化；Omnibus 放寬</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>CAC 回到 €120 時單戶淨值趨近零</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>見 D 段門檻</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>對手反應速度</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>慢（需電池工程 + 法定生產者 + 通路）</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>快（硬體一週可複製；Giant／Decathlon 一季推 €499 級）</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>與 8/28 原則</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>完全符合</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>抵觸「不重資產」除非 SPV；毛利 15% 門檻第四年才過</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>右尾（第 5 年後）</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>小：受 OEM 家數與窗口限制</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>大：訂閱裝機量複利，50 萬戶 ARR 約 NT$2B</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>D. 決策門檻（B2C 放大前必須同時通過；藍字填入試點實測值）</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>門檻</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>門檻值</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>試點實測（填入）</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr"/>
+      <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>CAC（€/戶，隨車或 B2B2C 通路）</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="D54" s="34" t="str">
+        <f>IF(C54&lt;=B54,"通過","未通過")</f>
+        <v>未通過</v>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>薪資扣抵／法人通路才壓得到；B2C 電商 €120 不成立</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>12 個月訂閱留存</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="34" t="str">
+        <f>IF(C55&gt;=B55,"通過","未通過")</f>
+        <v>未通過</v>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>2,000 台試點；低於 75% 單戶淨值轉薄</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>電池資產由 SPV 或租賃夥伴持有（1 = 是）</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="34" t="str">
+        <f>IF(C56&gt;=B56,"通過","未通過")</f>
+        <v>未通過</v>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>不重資產原則</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>種子車隊 duty cycle：日均 &lt;15 km 占比</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="34" t="str">
+        <f>IF(C57&gt;=B57,"通過","未通過")</f>
+        <v>未通過</v>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>支持 180／252／360Wh 分群，決定 RMB 117 槓桿</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>100k 量級 NT$6,000 隱含毛利（報價覆寫後）</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="D58" s="34" t="str">
+        <f>IF(C58&gt;=B58,"通過","未通過")</f>
+        <v>通過</v>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>第一份模型 BOM 表 E40（台越廠 100k）；三檔書面報價後重算</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>綜合判定</t>
+        </is>
+      </c>
+      <c r="D59" s="34" t="str">
+        <f>IF(COUNTIF(D54:D58,"通過")=5,"B2C 放大","B2C 停在 PB 通路 ODM 與 B2B 車隊；C1 為主業")</f>
+        <v>B2C 停在 PB 通路 ODM 與 B2B 車隊；C1 為主業</v>
+      </c>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>五項全過才放大；目前實測欄為預設值，須以試點數據覆寫</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>E. C1 的三個終止訊號</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n"/>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="n"/>
+      <c r="E61" s="4" t="n"/>
+      <c r="F61" s="4" t="n"/>
+      <c r="G61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Omnibus VIII 定案後再延或放寬護照／可換性 → 2027 談判槓桿消失，服務費只剩 EPR 行政價</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>BMZ 或 Bafang 歐洲實體在 2027 前推出「電池 + 護照 + 備品」套餐 → 整合空白被填掉</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>達方歐洲實體不承擔生產者的財務與法律責任 → 合規只能當代辦，鎖定效果減半</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>F. TAM／SAM／SOM（B2C，台/年，估）</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>層級</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>歐洲</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>台灣</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr"/>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>依據</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>傳統（非電動）自行車年銷量</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>400000</v>
+      </c>
+      <c r="E68" s="24">
+        <f>SUM(B68:D68)</f>
+        <v>12400000.0</v>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>歐洲總量 12–13M 扣 e-bike 4.5–5M；日本由電助力 78 萬台占 16% 反推；台灣無統計</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>都會通勤、€400–800／¥25–45k 價格帶（SAM）</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E69" s="24">
+        <f>SUM(B69:D69)</f>
+        <v>4700000.0</v>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>估：約三至五成</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>五年可取得 2%（SOM 低）</t>
+        </is>
+      </c>
+      <c r="B70" s="12">
+        <f>B69*0.02</f>
+        <v>50000.0</v>
+      </c>
+      <c r="C70" s="12">
+        <f>C69*0.02</f>
+        <v>40000.0</v>
+      </c>
+      <c r="D70" s="12">
+        <f>D69*0.02</f>
+        <v>4000.0</v>
+      </c>
+      <c r="E70" s="24">
+        <f>SUM(B70:D70)</f>
+        <v>94000.0</v>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>＝ SAM × 2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>五年可取得 5%（SOM 高）</t>
+        </is>
+      </c>
+      <c r="B71" s="12">
+        <f>B69*0.05</f>
+        <v>125000.0</v>
+      </c>
+      <c r="C71" s="12">
+        <f>C69*0.05</f>
+        <v>100000.0</v>
+      </c>
+      <c r="D71" s="12">
+        <f>D69*0.05</f>
+        <v>10000.0</v>
+      </c>
+      <c r="E71" s="24">
+        <f>SUM(B71:D71)</f>
+        <v>235000.0</v>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>＝ SAM × 5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>SAM 金額（車體 + 首年訂閱，NT$M）</t>
+        </is>
+      </c>
+      <c r="B72" s="12">
+        <f>B69*(入手價!B17+電池訂閱費!C19*12)*$B$11/1000000</f>
+        <v>37148.73871306808</v>
+      </c>
+      <c r="C72" s="12">
+        <f>C69*(入手價!B30+電池訂閱費!C61*12)/假設!$B$21*假設!$B$20/1000000</f>
+        <v>24738.60109894281</v>
+      </c>
+      <c r="D72" s="12">
+        <f>D69*(入手價!C17+電池訂閱費!C40*12)/1000000</f>
+        <v>2150.5837920424406</v>
+      </c>
+      <c r="E72" s="13">
+        <f>SUM(B72:D72)</f>
+        <v>64037.92360405333</v>
+      </c>
+      <c r="G72" s="11" t="inlineStr">
+        <is>
+          <t>逆向打擊傳統車只在歐洲成立（入手價 &lt; 一般自行車均價）；日本打的是電助力車</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>